--- a/Calendario.xlsx
+++ b/Calendario.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruna.marques\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520B94C0-6B95-4330-BD94-894A38A8869D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CF8F79-2CFF-4CFD-B082-39A1B687766D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CA38C382-423D-4205-ABE3-76963B1904F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$20</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="16">
   <si>
     <t>Produto</t>
   </si>
@@ -59,9 +62,6 @@
     <t>Processo Prorrogados</t>
   </si>
   <si>
-    <t>Prouni</t>
-  </si>
-  <si>
     <t>Bolsa permanência</t>
   </si>
   <si>
@@ -78,6 +78,15 @@
   </si>
   <si>
     <t>POEB</t>
+  </si>
+  <si>
+    <t>PROJETO</t>
+  </si>
+  <si>
+    <t>PROUNI</t>
+  </si>
+  <si>
+    <t>PROJETO BRUNA TESTE</t>
   </si>
 </sst>
 </file>
@@ -450,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB200F04-483A-4475-9B32-4D7557A6197E}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.453125" customWidth="1"/>
@@ -503,10 +512,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1">
         <v>46023</v>
@@ -517,10 +526,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1">
         <v>46054</v>
@@ -534,7 +543,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1">
         <v>46157</v>
@@ -545,10 +554,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1">
         <v>46157</v>
@@ -562,7 +571,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1">
         <v>46023</v>
@@ -576,7 +585,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1">
         <v>46113</v>
@@ -587,10 +596,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1">
         <v>46082</v>
@@ -601,10 +610,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1">
         <v>46113</v>
@@ -615,10 +624,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1">
         <v>46143</v>
@@ -629,10 +638,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>46174</v>
@@ -643,10 +652,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1">
         <v>46204</v>
@@ -657,10 +666,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="1">
         <v>46235</v>
@@ -671,10 +680,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1">
         <v>46266</v>
@@ -685,10 +694,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1">
         <v>46296</v>
@@ -699,10 +708,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1">
         <v>46142</v>
@@ -713,10 +722,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" s="1">
         <v>46295</v>
@@ -725,7 +734,22 @@
         <v>46296</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D20" s="1">
+        <v>46127</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D20" xr:uid="{DB200F04-483A-4475-9B32-4D7557A6197E}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Calendario.xlsx
+++ b/Calendario.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruna.marques\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CF8F79-2CFF-4CFD-B082-39A1B687766D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A206FA29-4693-4342-8635-05ECBCFF2470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CA38C382-423D-4205-ABE3-76963B1904F1}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$74</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="36">
   <si>
     <t>Produto</t>
   </si>
@@ -53,6 +53,9 @@
     <t>Data final</t>
   </si>
   <si>
+    <t xml:space="preserve">*as datas informadas são previsões </t>
+  </si>
+  <si>
     <t>FIES</t>
   </si>
   <si>
@@ -62,31 +65,88 @@
     <t>Processo Prorrogados</t>
   </si>
   <si>
+    <t>Oferta FIES Regular</t>
+  </si>
+  <si>
+    <t>Dilatação</t>
+  </si>
+  <si>
+    <t>Atualização balanço e DRE</t>
+  </si>
+  <si>
+    <t>PROUNI</t>
+  </si>
+  <si>
     <t>Bolsa permanência</t>
   </si>
   <si>
-    <t>Oferta fies</t>
+    <t>POEB</t>
+  </si>
+  <si>
+    <t>Processo Seletivo</t>
+  </si>
+  <si>
+    <t>Confraternização Universal</t>
+  </si>
+  <si>
+    <t>Paixão de Cristo (Sexta-feira Santa)</t>
+  </si>
+  <si>
+    <t>Tiradentes</t>
+  </si>
+  <si>
+    <t>Dia Mundial do Trabalho</t>
+  </si>
+  <si>
+    <t>Assunção de Nossa Senhora (feriado em BH)</t>
+  </si>
+  <si>
+    <t>Independência do Brasil</t>
+  </si>
+  <si>
+    <t>Nossa Senhora Aparecida</t>
+  </si>
+  <si>
+    <t>Finados</t>
+  </si>
+  <si>
+    <t>Proclamação da República</t>
+  </si>
+  <si>
+    <t>Dia Nacional de Zumbi e da Consciência Negra</t>
+  </si>
+  <si>
+    <t>Imaculada Conceição (feriado em BH)</t>
+  </si>
+  <si>
+    <t>Natal</t>
   </si>
   <si>
     <t>Adesão PROUNI</t>
   </si>
   <si>
-    <t>Dilatação</t>
-  </si>
-  <si>
-    <t>Atualização balanço e DRE</t>
-  </si>
-  <si>
-    <t>POEB</t>
-  </si>
-  <si>
-    <t>PROJETO</t>
-  </si>
-  <si>
-    <t>PROUNI</t>
-  </si>
-  <si>
-    <t>PROJETO BRUNA TESTE</t>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Processo Seletivo Regular</t>
+  </si>
+  <si>
+    <t>Oferta FIES Remanescente</t>
+  </si>
+  <si>
+    <t>Manutenção PROUNI</t>
+  </si>
+  <si>
+    <t>Processo Seletivo Remanescente</t>
+  </si>
+  <si>
+    <t>Gestão Acessos IES e Mantenedora FIES</t>
+  </si>
+  <si>
+    <t>Corpus Christi</t>
+  </si>
+  <si>
+    <t>Carnaval</t>
   </si>
 </sst>
 </file>
@@ -122,9 +182,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,16 +522,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB200F04-483A-4475-9B32-4D7557A6197E}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.453125" customWidth="1"/>
-    <col min="2" max="2" width="28.7265625" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" customWidth="1"/>
+    <col min="2" max="2" width="42.90625" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" customWidth="1"/>
     <col min="4" max="4" width="18.81640625" customWidth="1"/>
+    <col min="7" max="7" width="31.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -481,275 +545,1436 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
-        <v>46041</v>
+        <v>46023</v>
       </c>
       <c r="D2" s="1">
-        <v>46173</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1">
-        <v>46036</v>
+        <v>46023</v>
       </c>
       <c r="D3" s="1">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>46023</v>
       </c>
       <c r="D4" s="1">
-        <v>46037</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46023</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1">
+        <v>46036</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46052</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1">
+        <v>46041</v>
+      </c>
+      <c r="D7" s="1">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C8" s="1">
+        <v>46048</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46055</v>
+      </c>
+      <c r="D10" s="1">
+        <v>46127</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1">
+        <v>46055</v>
+      </c>
+      <c r="D11" s="1">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46069</v>
+      </c>
+      <c r="D12" s="1">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46069</v>
+      </c>
+      <c r="D13" s="1">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46082</v>
+      </c>
+      <c r="D14" s="1">
+        <v>46096</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46083</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46113</v>
+      </c>
+      <c r="D16" s="1">
+        <v>46143</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46113</v>
+      </c>
+      <c r="D17" s="1">
+        <v>46127</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46115</v>
+      </c>
+      <c r="D18" s="1">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46115</v>
+      </c>
+      <c r="D19" s="1">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D20" s="1">
+        <v>46122</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D21" s="1">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D22" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D23" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="1">
+        <v>46134</v>
+      </c>
+      <c r="D24" s="1">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46139</v>
+      </c>
+      <c r="D25" s="1">
+        <v>46143</v>
+      </c>
+      <c r="E25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D26" s="1">
+        <v>46149</v>
+      </c>
+      <c r="E26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46143</v>
+      </c>
+      <c r="D27" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46143</v>
+      </c>
+      <c r="D28" s="1">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="1">
+        <v>46143</v>
+      </c>
+      <c r="D29" s="1">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46146</v>
+      </c>
+      <c r="D30" s="1">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46157</v>
+      </c>
+      <c r="D31" s="1">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="1">
+        <v>46157</v>
+      </c>
+      <c r="D32" s="1">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D33" s="1">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D34" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D35" s="1">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D36" s="1">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D37" s="1">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="1">
-        <v>46054</v>
-      </c>
-      <c r="D5" s="1">
-        <v>46068</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1">
-        <v>46157</v>
-      </c>
-      <c r="D6" s="1">
-        <v>46203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="C38" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D38" s="1">
+        <v>45848</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D39" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D40" s="1">
+        <v>46295</v>
+      </c>
+      <c r="E40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1">
-        <v>46157</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46203</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="1">
-        <v>46023</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46037</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="1">
-        <v>46113</v>
-      </c>
-      <c r="D9" s="1">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1">
-        <v>46082</v>
-      </c>
-      <c r="D10" s="1">
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1">
-        <v>46113</v>
-      </c>
-      <c r="D11" s="1">
-        <v>46127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="1">
-        <v>46143</v>
-      </c>
-      <c r="D12" s="1">
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1">
-        <v>46174</v>
-      </c>
-      <c r="D13" s="1">
-        <v>46188</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="C41" s="1">
         <v>46204</v>
       </c>
-      <c r="D14" s="1">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="1">
+      <c r="D41" s="1">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D42" s="1">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D43" s="1">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="1">
         <v>46235</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D44" s="1">
         <v>46249</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="1">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="1">
+        <v>46237</v>
+      </c>
+      <c r="D45" s="1">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="1">
+        <v>46249</v>
+      </c>
+      <c r="D46" s="1">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="1">
+        <v>46249</v>
+      </c>
+      <c r="D47" s="1">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="1">
         <v>46266</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D48" s="1">
         <v>46280</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="1">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="1">
+        <v>46272</v>
+      </c>
+      <c r="D49" s="1">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="1">
+        <v>46272</v>
+      </c>
+      <c r="D50" s="1">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="1">
+        <v>46272</v>
+      </c>
+      <c r="D51" s="1">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="1">
+        <v>46286</v>
+      </c>
+      <c r="D52" s="1">
+        <v>46303</v>
+      </c>
+      <c r="E52" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D53" s="1">
         <v>46296</v>
       </c>
-      <c r="D17" s="1">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D54" s="1">
         <v>46310</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D55" s="1">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" s="1">
+        <v>46300</v>
+      </c>
+      <c r="D56" s="1">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="1">
+        <v>46307</v>
+      </c>
+      <c r="D57" s="1">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" s="1">
+        <v>46307</v>
+      </c>
+      <c r="D58" s="1">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59" s="1">
+        <v>46318</v>
+      </c>
+      <c r="D59" s="1">
+        <v>46354</v>
+      </c>
+      <c r="E59" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="1">
-        <v>46142</v>
-      </c>
-      <c r="D18" s="1">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C60" s="1">
+        <v>46327</v>
+      </c>
+      <c r="D60" s="1">
+        <v>46341</v>
+      </c>
+      <c r="E60" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="1">
+        <v>46328</v>
+      </c>
+      <c r="D61" s="1">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="1">
+        <v>46328</v>
+      </c>
+      <c r="D62" s="1">
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="1">
+        <v>46328</v>
+      </c>
+      <c r="D63" s="1">
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="1">
+        <v>46341</v>
+      </c>
+      <c r="D64" s="1">
+        <v>46341</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" s="1">
+        <v>46341</v>
+      </c>
+      <c r="D65" s="1">
+        <v>46341</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="1">
+        <v>46346</v>
+      </c>
+      <c r="D66" s="1">
+        <v>46346</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="1">
+        <v>46346</v>
+      </c>
+      <c r="D67" s="1">
+        <v>46346</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" s="1">
+        <v>46349</v>
+      </c>
+      <c r="D68" s="1">
+        <v>46374</v>
+      </c>
+      <c r="E68" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="1">
-        <v>46295</v>
-      </c>
-      <c r="D19" s="1">
-        <v>46296</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="1">
-        <v>46122</v>
-      </c>
-      <c r="D20" s="1">
-        <v>46127</v>
+      <c r="C69" s="1">
+        <v>46357</v>
+      </c>
+      <c r="D69" s="1">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70" s="1">
+        <v>46363</v>
+      </c>
+      <c r="D70" s="1">
+        <v>46367</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" s="1">
+        <v>46364</v>
+      </c>
+      <c r="D71" s="1">
+        <v>46364</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72" s="1">
+        <v>46364</v>
+      </c>
+      <c r="D72" s="1">
+        <v>46364</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" s="1">
+        <v>46381</v>
+      </c>
+      <c r="D73" s="1">
+        <v>46381</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" s="1">
+        <v>46381</v>
+      </c>
+      <c r="D74" s="1">
+        <v>46381</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D20" xr:uid="{DB200F04-483A-4475-9B32-4D7557A6197E}"/>
+  <autoFilter ref="A1:E74" xr:uid="{DB200F04-483A-4475-9B32-4D7557A6197E}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E74">
+      <sortCondition ref="C1:C74"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="9e817275-3ca7-4cc1-a27e-5edb63184867" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e817275-3ca7-4cc1-a27e-5edb63184867">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="617798ea-9269-4e63-957b-1b0af4f67144" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B1AB1F88DD0E424CBFC219C2F59A034B" ma:contentTypeVersion="22" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="ab2017a52bd3b6fff4077d7e60210ac4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="9e817275-3ca7-4cc1-a27e-5edb63184867" xmlns:ns3="617798ea-9269-4e63-957b-1b0af4f67144" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1fe1ad2d79e67dd942d8744afbdaefaf" ns1:_="" ns2:_="" ns3:_="">
+    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
+    <xsd:import namespace="9e817275-3ca7-4cc1-a27e-5edb63184867"/>
+    <xsd:import namespace="617798ea-9269-4e63-957b-1b0af4f67144"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="28" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="29" nillable="true" ma:displayName="Ação de Interface do Usuário da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9e817275-3ca7-4cc1-a27e-5edb63184867" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4b2e35d7-0bf6-4cd4-a167-eb472820a88d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="21" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="22" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="23" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_Flow_SignoffStatus" ma:index="25" nillable="true" ma:displayName="Status de liberação" ma:indexed="true" ma:internalName="Status_x0020_de_x0020_libera_x00e7__x00e3_o">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="27" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="617798ea-9269-4e63-957b-1b0af4f67144" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b2a6ccf0-5777-42d5-b4f8-3baeadfcf273}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="617798ea-9269-4e63-957b-1b0af4f67144">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54A84ECE-BAFE-4091-97FC-0905577711DD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="617798ea-9269-4e63-957b-1b0af4f67144"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="9e817275-3ca7-4cc1-a27e-5edb63184867"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB807947-B0B3-4D3E-914D-CECAFAB71D49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9e817275-3ca7-4cc1-a27e-5edb63184867"/>
+    <ds:schemaRef ds:uri="617798ea-9269-4e63-957b-1b0af4f67144"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33B338B4-8CA0-4C4E-9D5F-720BBB79F162}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{60bcece8-eb6b-494e-a607-e83fcdcef333}" enabled="0" method="" siteId="{60bcece8-eb6b-494e-a607-e83fcdcef333}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/Calendario.xlsx
+++ b/Calendario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruna.marques\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A206FA29-4693-4342-8635-05ECBCFF2470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70379D5-97E2-48BF-953F-1175D899CD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CA38C382-423D-4205-ABE3-76963B1904F1}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$75</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="21">
   <si>
     <t>Produto</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Data final</t>
   </si>
   <si>
-    <t xml:space="preserve">*as datas informadas são previsões </t>
-  </si>
-  <si>
     <t>FIES</t>
   </si>
   <si>
@@ -86,48 +83,9 @@
     <t>Processo Seletivo</t>
   </si>
   <si>
-    <t>Confraternização Universal</t>
-  </si>
-  <si>
-    <t>Paixão de Cristo (Sexta-feira Santa)</t>
-  </si>
-  <si>
-    <t>Tiradentes</t>
-  </si>
-  <si>
-    <t>Dia Mundial do Trabalho</t>
-  </si>
-  <si>
-    <t>Assunção de Nossa Senhora (feriado em BH)</t>
-  </si>
-  <si>
-    <t>Independência do Brasil</t>
-  </si>
-  <si>
-    <t>Nossa Senhora Aparecida</t>
-  </si>
-  <si>
-    <t>Finados</t>
-  </si>
-  <si>
-    <t>Proclamação da República</t>
-  </si>
-  <si>
-    <t>Dia Nacional de Zumbi e da Consciência Negra</t>
-  </si>
-  <si>
-    <t>Imaculada Conceição (feriado em BH)</t>
-  </si>
-  <si>
-    <t>Natal</t>
-  </si>
-  <si>
     <t>Adesão PROUNI</t>
   </si>
   <si>
-    <t>*</t>
-  </si>
-  <si>
     <t>Processo Seletivo Regular</t>
   </si>
   <si>
@@ -143,10 +101,7 @@
     <t>Gestão Acessos IES e Mantenedora FIES</t>
   </si>
   <si>
-    <t>Corpus Christi</t>
-  </si>
-  <si>
-    <t>Carnaval</t>
+    <t>FERIADO</t>
   </si>
 </sst>
 </file>
@@ -522,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB200F04-483A-4475-9B32-4D7557A6197E}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.453125" customWidth="1"/>
@@ -532,7 +487,7 @@
     <col min="7" max="7" width="31.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -545,19 +500,13 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1">
         <v>46023</v>
@@ -566,12 +515,12 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
       </c>
       <c r="C3" s="1">
         <v>46023</v>
@@ -580,12 +529,12 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1">
         <v>46023</v>
@@ -594,12 +543,12 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1">
         <v>46023</v>
@@ -608,12 +557,12 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1">
         <v>46036</v>
@@ -622,12 +571,12 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
       </c>
       <c r="C7" s="1">
         <v>46041</v>
@@ -636,12 +585,12 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="1">
         <v>46048</v>
@@ -650,12 +599,12 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
         <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>46054</v>
@@ -664,12 +613,12 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <v>46055</v>
@@ -677,16 +626,13 @@
       <c r="D10" s="1">
         <v>46127</v>
       </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1">
         <v>46055</v>
@@ -695,12 +641,12 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1">
         <v>46069</v>
@@ -709,12 +655,12 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1">
         <v>46069</v>
@@ -723,12 +669,12 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
         <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
       </c>
       <c r="C14" s="1">
         <v>46082</v>
@@ -736,16 +682,13 @@
       <c r="D14" s="1">
         <v>46096</v>
       </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C15" s="1">
         <v>46083</v>
@@ -754,12 +697,12 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" s="1">
         <v>46113</v>
@@ -767,16 +710,13 @@
       <c r="D16" s="1">
         <v>46143</v>
       </c>
-      <c r="E16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
         <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
       </c>
       <c r="C17" s="1">
         <v>46113</v>
@@ -784,16 +724,13 @@
       <c r="D17" s="1">
         <v>46127</v>
       </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1">
         <v>46115</v>
@@ -802,12 +739,12 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C19" s="1">
         <v>46115</v>
@@ -816,12 +753,12 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1">
         <v>46118</v>
@@ -829,16 +766,13 @@
       <c r="D20" s="1">
         <v>46122</v>
       </c>
-      <c r="E20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C21" s="1">
         <v>46118</v>
@@ -847,12 +781,12 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1">
         <v>46133</v>
@@ -861,12 +795,12 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C23" s="1">
         <v>46133</v>
@@ -875,12 +809,12 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C24" s="1">
         <v>46134</v>
@@ -889,12 +823,12 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" s="1">
         <v>46139</v>
@@ -902,16 +836,13 @@
       <c r="D25" s="1">
         <v>46143</v>
       </c>
-      <c r="E25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C26" s="1">
         <v>46141</v>
@@ -919,16 +850,13 @@
       <c r="D26" s="1">
         <v>46149</v>
       </c>
-      <c r="E26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" t="s">
         <v>11</v>
-      </c>
-      <c r="B27" t="s">
-        <v>12</v>
       </c>
       <c r="C27" s="1">
         <v>46143</v>
@@ -937,12 +865,12 @@
         <v>46157</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C28" s="1">
         <v>46143</v>
@@ -951,12 +879,12 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C29" s="1">
         <v>46143</v>
@@ -965,12 +893,12 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C30" s="1">
         <v>46146</v>
@@ -979,12 +907,12 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="1">
         <v>46157</v>
@@ -993,12 +921,12 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C32" s="1">
         <v>46157</v>
@@ -1007,12 +935,12 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
         <v>11</v>
-      </c>
-      <c r="B33" t="s">
-        <v>12</v>
       </c>
       <c r="C33" s="1">
         <v>46174</v>
@@ -1021,12 +949,12 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34" s="1">
         <v>46174</v>
@@ -1035,12 +963,12 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C35" s="1">
         <v>46174</v>
@@ -1049,12 +977,12 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C36" s="1">
         <v>46177</v>
@@ -1063,12 +991,12 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C37" s="1">
         <v>46177</v>
@@ -1077,12 +1005,12 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" s="1">
         <v>46197</v>
@@ -1091,12 +1019,12 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" t="s">
         <v>11</v>
-      </c>
-      <c r="B39" t="s">
-        <v>12</v>
       </c>
       <c r="C39" s="1">
         <v>46204</v>
@@ -1105,12 +1033,12 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C40" s="1">
         <v>46204</v>
@@ -1118,16 +1046,13 @@
       <c r="D40" s="1">
         <v>46295</v>
       </c>
-      <c r="E40" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C41" s="1">
         <v>46204</v>
@@ -1136,12 +1061,12 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
         <v>5</v>
-      </c>
-      <c r="B42" t="s">
-        <v>6</v>
       </c>
       <c r="C42" s="1">
         <v>46204</v>
@@ -1150,12 +1075,12 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C43" s="1">
         <v>46209</v>
@@ -1164,12 +1089,12 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" t="s">
         <v>11</v>
-      </c>
-      <c r="B44" t="s">
-        <v>12</v>
       </c>
       <c r="C44" s="1">
         <v>46235</v>
@@ -1178,12 +1103,12 @@
         <v>46249</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C45" s="1">
         <v>46237</v>
@@ -1192,12 +1117,12 @@
         <v>46241</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C46" s="1">
         <v>46249</v>
@@ -1206,12 +1131,12 @@
         <v>46249</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C47" s="1">
         <v>46249</v>
@@ -1220,12 +1145,12 @@
         <v>46249</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="s">
         <v>11</v>
-      </c>
-      <c r="B48" t="s">
-        <v>12</v>
       </c>
       <c r="C48" s="1">
         <v>46266</v>
@@ -1234,12 +1159,12 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C49" s="1">
         <v>46272</v>
@@ -1248,9 +1173,9 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B50" t="s">
         <v>20</v>
@@ -1262,9 +1187,9 @@
         <v>46272</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B51" t="s">
         <v>20</v>
@@ -1276,12 +1201,12 @@
         <v>46272</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C52" s="1">
         <v>46286</v>
@@ -1289,16 +1214,13 @@
       <c r="D52" s="1">
         <v>46303</v>
       </c>
-      <c r="E52" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53" s="1">
         <v>46295</v>
@@ -1307,12 +1229,12 @@
         <v>46296</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" t="s">
         <v>11</v>
-      </c>
-      <c r="B54" t="s">
-        <v>12</v>
       </c>
       <c r="C54" s="1">
         <v>46296</v>
@@ -1321,12 +1243,12 @@
         <v>46310</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1">
         <v>46296</v>
@@ -1335,12 +1257,12 @@
         <v>46303</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C56" s="1">
         <v>46300</v>
@@ -1349,12 +1271,12 @@
         <v>46304</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C57" s="1">
         <v>46307</v>
@@ -1363,12 +1285,12 @@
         <v>46307</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C58" s="1">
         <v>46307</v>
@@ -1377,12 +1299,12 @@
         <v>46307</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1">
         <v>46318</v>
@@ -1390,16 +1312,13 @@
       <c r="D59" s="1">
         <v>46354</v>
       </c>
-      <c r="E59" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" t="s">
         <v>11</v>
-      </c>
-      <c r="B60" t="s">
-        <v>12</v>
       </c>
       <c r="C60" s="1">
         <v>46327</v>
@@ -1407,16 +1326,13 @@
       <c r="D60" s="1">
         <v>46341</v>
       </c>
-      <c r="E60" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C61" s="1">
         <v>46328</v>
@@ -1425,12 +1341,12 @@
         <v>46332</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B62" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C62" s="1">
         <v>46328</v>
@@ -1439,12 +1355,12 @@
         <v>46328</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C63" s="1">
         <v>46328</v>
@@ -1453,12 +1369,12 @@
         <v>46328</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C64" s="1">
         <v>46341</v>
@@ -1467,12 +1383,12 @@
         <v>46341</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C65" s="1">
         <v>46341</v>
@@ -1481,12 +1397,12 @@
         <v>46341</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C66" s="1">
         <v>46346</v>
@@ -1495,12 +1411,12 @@
         <v>46346</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C67" s="1">
         <v>46346</v>
@@ -1509,29 +1425,26 @@
         <v>46346</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C68" s="1">
-        <v>46349</v>
+        <v>46330</v>
       </c>
       <c r="D68" s="1">
         <v>46374</v>
       </c>
-      <c r="E68" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69" t="s">
         <v>11</v>
-      </c>
-      <c r="B69" t="s">
-        <v>12</v>
       </c>
       <c r="C69" s="1">
         <v>46357</v>
@@ -1540,12 +1453,12 @@
         <v>46371</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C70" s="1">
         <v>46363</v>
@@ -1554,12 +1467,12 @@
         <v>46367</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C71" s="1">
         <v>46364</v>
@@ -1568,12 +1481,12 @@
         <v>46364</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B72" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C72" s="1">
         <v>46364</v>
@@ -1582,12 +1495,12 @@
         <v>46364</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C73" s="1">
         <v>46381</v>
@@ -1596,12 +1509,12 @@
         <v>46381</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C74" s="1">
         <v>46381</v>
@@ -1610,12 +1523,22 @@
         <v>46381</v>
       </c>
     </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="1">
+        <v>46336</v>
+      </c>
+      <c r="D75" s="1">
+        <v>46374</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E74" xr:uid="{DB200F04-483A-4475-9B32-4D7557A6197E}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E74">
-      <sortCondition ref="C1:C74"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:E75" xr:uid="{DB200F04-483A-4475-9B32-4D7557A6197E}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -1635,6 +1558,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B1AB1F88DD0E424CBFC219C2F59A034B" ma:contentTypeVersion="22" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="ab2017a52bd3b6fff4077d7e60210ac4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="9e817275-3ca7-4cc1-a27e-5edb63184867" xmlns:ns3="617798ea-9269-4e63-957b-1b0af4f67144" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1fe1ad2d79e67dd942d8744afbdaefaf" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1918,15 +1850,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54A84ECE-BAFE-4091-97FC-0905577711DD}">
   <ds:schemaRefs>
@@ -1946,6 +1869,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33B338B4-8CA0-4C4E-9D5F-720BBB79F162}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB807947-B0B3-4D3E-914D-CECAFAB71D49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1965,14 +1896,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33B338B4-8CA0-4C4E-9D5F-720BBB79F162}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{60bcece8-eb6b-494e-a607-e83fcdcef333}" enabled="0" method="" siteId="{60bcece8-eb6b-494e-a607-e83fcdcef333}" removed="1"/>

--- a/Calendario.xlsx
+++ b/Calendario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruna.marques\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70379D5-97E2-48BF-953F-1175D899CD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E83081-216A-47B3-A73B-B0A3B7B6DA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CA38C382-423D-4205-ABE3-76963B1904F1}"/>
   </bookViews>
@@ -137,12 +137,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB200F04-483A-4475-9B32-4D7557A6197E}">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.453125" customWidth="1"/>
@@ -760,11 +762,11 @@
       <c r="B20" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="1">
-        <v>46118</v>
-      </c>
-      <c r="D20" s="1">
-        <v>46122</v>
+      <c r="C20" s="4">
+        <v>46114</v>
+      </c>
+      <c r="D20" s="4">
+        <v>46125</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -816,11 +818,11 @@
       <c r="B24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="1">
-        <v>46134</v>
-      </c>
-      <c r="D24" s="1">
-        <v>46172</v>
+      <c r="C24" s="4">
+        <v>46148</v>
+      </c>
+      <c r="D24" s="4">
+        <v>46164</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -915,10 +917,10 @@
         <v>7</v>
       </c>
       <c r="C31" s="1">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="D31" s="1">
-        <v>46203</v>
+        <v>46189</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -929,10 +931,10 @@
         <v>14</v>
       </c>
       <c r="C32" s="1">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="D32" s="1">
-        <v>46203</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -1159,7 +1161,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -1173,7 +1175,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -1187,7 +1189,7 @@
         <v>46272</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>10</v>
       </c>
@@ -1201,7 +1203,7 @@
         <v>46272</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>10</v>
       </c>
@@ -1215,7 +1217,7 @@
         <v>46303</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>10</v>
       </c>
@@ -1229,7 +1231,7 @@
         <v>46296</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>10</v>
       </c>
@@ -1243,21 +1245,21 @@
         <v>46310</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>4</v>
       </c>
       <c r="B55" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="4">
         <v>46296</v>
       </c>
-      <c r="D55" s="1">
-        <v>46303</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D55" s="4">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -1271,7 +1273,7 @@
         <v>46304</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -1285,7 +1287,7 @@
         <v>46307</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -1299,21 +1301,23 @@
         <v>46307</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>4</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="1">
-        <v>46318</v>
-      </c>
-      <c r="D59" s="1">
-        <v>46354</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C59" s="4">
+        <v>45965</v>
+      </c>
+      <c r="D59" s="4">
+        <v>46353</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -1327,7 +1331,7 @@
         <v>46341</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -1341,7 +1345,7 @@
         <v>46332</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -1355,7 +1359,7 @@
         <v>46328</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -1369,7 +1373,7 @@
         <v>46328</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -1433,7 +1437,7 @@
         <v>14</v>
       </c>
       <c r="C68" s="1">
-        <v>46330</v>
+        <v>46350</v>
       </c>
       <c r="D68" s="1">
         <v>46374</v>
@@ -1531,10 +1535,10 @@
         <v>7</v>
       </c>
       <c r="C75" s="1">
-        <v>46336</v>
+        <v>46353</v>
       </c>
       <c r="D75" s="1">
-        <v>46374</v>
+        <v>46368</v>
       </c>
     </row>
   </sheetData>
@@ -1558,15 +1562,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B1AB1F88DD0E424CBFC219C2F59A034B" ma:contentTypeVersion="22" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="ab2017a52bd3b6fff4077d7e60210ac4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="9e817275-3ca7-4cc1-a27e-5edb63184867" xmlns:ns3="617798ea-9269-4e63-957b-1b0af4f67144" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1fe1ad2d79e67dd942d8744afbdaefaf" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1850,6 +1845,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54A84ECE-BAFE-4091-97FC-0905577711DD}">
   <ds:schemaRefs>
@@ -1869,14 +1873,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33B338B4-8CA0-4C4E-9D5F-720BBB79F162}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB807947-B0B3-4D3E-914D-CECAFAB71D49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1896,6 +1892,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33B338B4-8CA0-4C4E-9D5F-720BBB79F162}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{60bcece8-eb6b-494e-a607-e83fcdcef333}" enabled="0" method="" siteId="{60bcece8-eb6b-494e-a607-e83fcdcef333}" removed="1"/>
